--- a/data/merged/2026-10-08/MERGED_UK_Mite-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_UK_Mite-Vacuum_2026-10-08.xlsx
@@ -1618,13 +1618,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1662,13 +1662,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1706,13 +1706,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1750,13 +1750,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1794,13 +1794,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1838,13 +1838,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1882,13 +1882,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2247,7 +2247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR16"/>
+  <dimension ref="A1:BR15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -3870,7 +3870,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTVR91</t>
+          <t>B0D7HF8S2W</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -3883,23 +3883,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>OSALADI 3pcs Vacuum Wall Support Plastic Vacuum Holder for Wall Mounted Use Cordless Accessories Supports for Home Cleaning</t>
+          <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine wi</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTVR91</t>
+          <t>B0D7HF8S2W</t>
         </is>
       </c>
       <c r="M8" s="14"/>
@@ -3915,13 +3915,19 @@
       <c r="W8" s="15"/>
       <c r="X8" s="15"/>
       <c r="Y8" s="19"/>
-      <c r="Z8" s="20"/>
+      <c r="Z8" s="20">
+        <v>21.55</v>
+      </c>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8" s="2"/>
-      <c r="AD8" s="19"/>
+      <c r="AD8" s="19">
+        <v>87</v>
+      </c>
       <c r="AE8" s="15"/>
-      <c r="AF8" s="21"/>
+      <c r="AF8" s="21">
+        <v>3.9</v>
+      </c>
       <c r="AG8" s="22">
         <v>0</v>
       </c>
@@ -3972,7 +3978,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B0D7HF8S2W</t>
+          <t>B0DSCSR4MB</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -3985,23 +3991,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine wi</t>
+          <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; SofasMite Level Display, UV-C Light &amp; Hot Air &amp; Roller</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B0D7HF8S2W</t>
+          <t>B0DSCSR4MB</t>
         </is>
       </c>
       <c r="M9" s="14"/>
@@ -4017,18 +4023,16 @@
       <c r="W9" s="15"/>
       <c r="X9" s="15"/>
       <c r="Y9" s="19"/>
-      <c r="Z9" s="20">
-        <v>21.55</v>
-      </c>
+      <c r="Z9" s="20"/>
       <c r="AA9"/>
       <c r="AB9"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="19">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="AE9" s="15"/>
       <c r="AF9" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG9" s="22">
         <v>0</v>
@@ -4080,104 +4084,216 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0DSCSR4MB</t>
+          <t>B0DSFM31F7</t>
         </is>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Tjean</t>
+        </is>
+      </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.ukundefined</t>
+          <t>https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; SofasMite Level Display, UV-C Light &amp; Hot Air &amp; Roller</t>
+          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, He</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0DSCSR4MB</t>
-        </is>
-      </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="18"/>
+          <t>B0DSFM31F7</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Futon Vacuums</t>
+        </is>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="O10" s="15">
+        <v>751605</v>
+      </c>
+      <c r="P10" s="15">
+        <v>16609</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="R10" s="17" t="inlineStr">
+        <is>
+          <t>Futon Vacuums</t>
+        </is>
+      </c>
+      <c r="S10" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="T10" s="15"/>
       <c r="U10" s="16"/>
       <c r="V10" s="15"/>
       <c r="W10" s="15"/>
       <c r="X10" s="15"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="20"/>
+      <c r="Y10" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="20">
+        <v>46.8</v>
+      </c>
       <c r="AA10"/>
       <c r="AB10"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="19">
-        <v>21</v>
-      </c>
-      <c r="AE10" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="AE10" s="15">
+        <v>0</v>
+      </c>
       <c r="AF10" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG10" s="22">
         <v>0</v>
       </c>
-      <c r="AH10" s="20"/>
+      <c r="AH10" s="20">
+        <v>3.42</v>
+      </c>
       <c r="AI10" s="16">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AJ10"/>
-      <c r="AK10" s="13"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="13"/>
+      <c r="AK10" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AL10" s="19">
+        <v>539</v>
+      </c>
+      <c r="AM10" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN10" s="13"/>
       <c r="AO10" s="13"/>
       <c r="AP10"/>
-      <c r="AQ10" s="19"/>
-      <c r="AR10" s="19"/>
-      <c r="AS10" s="14"/>
-      <c r="AT10" s="13"/>
-      <c r="AU10" s="13"/>
-      <c r="AV10" s="14"/>
-      <c r="AW10" s="13"/>
+      <c r="AQ10" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="14" t="inlineStr">
+        <is>
+          <t>TJean Store</t>
+        </is>
+      </c>
+      <c r="AT10" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU10" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV10" s="14" t="inlineStr">
+        <is>
+          <t>杭州市 余杭区 浙江省 311100 CN</t>
+        </is>
+      </c>
+      <c r="AW10" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP</t>
+        </is>
+      </c>
       <c r="AX10" s="13"/>
       <c r="AY10" s="13"/>
       <c r="AZ10" s="13"/>
       <c r="BA10" s="13"/>
       <c r="BB10" s="13"/>
-      <c r="BC10" s="13"/>
-      <c r="BD10" s="13"/>
+      <c r="BC10" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD10" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE10" s="13"/>
       <c r="BF10" s="13"/>
       <c r="BG10" s="13"/>
       <c r="BH10" s="14"/>
       <c r="BI10" s="23"/>
-      <c r="BJ10" s="23"/>
-      <c r="BK10" s="23"/>
-      <c r="BL10" s="23"/>
-      <c r="BM10" s="23"/>
-      <c r="BN10" s="23"/>
-      <c r="BO10" s="23"/>
-      <c r="BP10" s="23"/>
-      <c r="BQ10" s="23"/>
-      <c r="BR10" s="13"/>
+      <c r="BJ10" s="23" t="inlineStr">
+        <is>
+          <t>2.22 kg</t>
+        </is>
+      </c>
+      <c r="BK10" s="23" t="inlineStr">
+        <is>
+          <t>2.22 kg</t>
+        </is>
+      </c>
+      <c r="BL10" s="23" t="inlineStr">
+        <is>
+          <t>24 x 19.5 x 28.5 cm</t>
+        </is>
+      </c>
+      <c r="BM10" s="23" t="inlineStr">
+        <is>
+          <t>24.00 x 19.50 x 28.50 cm</t>
+        </is>
+      </c>
+      <c r="BN10" s="23" t="inlineStr">
+        <is>
+          <t>2.22 kg</t>
+        </is>
+      </c>
+      <c r="BO10" s="23" t="inlineStr">
+        <is>
+          <t>2.22 kg</t>
+        </is>
+      </c>
+      <c r="BP10" s="23" t="inlineStr">
+        <is>
+          <t>32.6 x 27.5 x 21.1 cm</t>
+        </is>
+      </c>
+      <c r="BQ10" s="23" t="inlineStr">
+        <is>
+          <t>32.60 x 27.50 x 21.10 cm</t>
+        </is>
+      </c>
+      <c r="BR10" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
@@ -4186,216 +4302,104 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
+          <t>B0DTS8VCFB</t>
         </is>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>Tjean</t>
-        </is>
-      </c>
+      <c r="F11" s="14"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.ukundefined</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, He</t>
+          <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; SofasUltrasonic Cleaning, UV-C Light &amp; Hot Air &amp; Roller</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Futon Vacuums</t>
-        </is>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O11" s="15">
-        <v>751605</v>
-      </c>
-      <c r="P11" s="15">
-        <v>16609</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="R11" s="17" t="inlineStr">
-        <is>
-          <t>Futon Vacuums</t>
-        </is>
-      </c>
-      <c r="S11" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>B0DTS8VCFB</t>
+        </is>
+      </c>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="15"/>
       <c r="U11" s="16"/>
       <c r="V11" s="15"/>
       <c r="W11" s="15"/>
       <c r="X11" s="15"/>
-      <c r="Y11" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="20">
-        <v>46.8</v>
-      </c>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="20"/>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11" s="2"/>
       <c r="AD11" s="19">
-        <v>29</v>
-      </c>
-      <c r="AE11" s="15">
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="AE11" s="15"/>
       <c r="AF11" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG11" s="22">
         <v>0</v>
       </c>
-      <c r="AH11" s="20">
-        <v>3.42</v>
-      </c>
+      <c r="AH11" s="20"/>
       <c r="AI11" s="16">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="AJ11"/>
-      <c r="AK11" s="13" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AL11" s="19">
-        <v>539</v>
-      </c>
-      <c r="AM11" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK11" s="13"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
       <c r="AO11" s="13"/>
       <c r="AP11"/>
-      <c r="AQ11" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="14" t="inlineStr">
-        <is>
-          <t>TJean Store</t>
-        </is>
-      </c>
-      <c r="AT11" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU11" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV11" s="14" t="inlineStr">
-        <is>
-          <t>杭州市 余杭区 浙江省 311100 CN</t>
-        </is>
-      </c>
-      <c r="AW11" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP</t>
-        </is>
-      </c>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="19"/>
+      <c r="AS11" s="14"/>
+      <c r="AT11" s="13"/>
+      <c r="AU11" s="13"/>
+      <c r="AV11" s="14"/>
+      <c r="AW11" s="13"/>
       <c r="AX11" s="13"/>
       <c r="AY11" s="13"/>
       <c r="AZ11" s="13"/>
       <c r="BA11" s="13"/>
       <c r="BB11" s="13"/>
-      <c r="BC11" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD11" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC11" s="13"/>
+      <c r="BD11" s="13"/>
       <c r="BE11" s="13"/>
       <c r="BF11" s="13"/>
       <c r="BG11" s="13"/>
       <c r="BH11" s="14"/>
       <c r="BI11" s="23"/>
-      <c r="BJ11" s="23" t="inlineStr">
-        <is>
-          <t>2.22 kg</t>
-        </is>
-      </c>
-      <c r="BK11" s="23" t="inlineStr">
-        <is>
-          <t>2.22 kg</t>
-        </is>
-      </c>
-      <c r="BL11" s="23" t="inlineStr">
-        <is>
-          <t>24 x 19.5 x 28.5 cm</t>
-        </is>
-      </c>
-      <c r="BM11" s="23" t="inlineStr">
-        <is>
-          <t>24.00 x 19.50 x 28.50 cm</t>
-        </is>
-      </c>
-      <c r="BN11" s="23" t="inlineStr">
-        <is>
-          <t>2.22 kg</t>
-        </is>
-      </c>
-      <c r="BO11" s="23" t="inlineStr">
-        <is>
-          <t>2.22 kg</t>
-        </is>
-      </c>
-      <c r="BP11" s="23" t="inlineStr">
-        <is>
-          <t>32.6 x 27.5 x 21.1 cm</t>
-        </is>
-      </c>
-      <c r="BQ11" s="23" t="inlineStr">
-        <is>
-          <t>32.60 x 27.50 x 21.10 cm</t>
-        </is>
-      </c>
-      <c r="BR11" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ11" s="23"/>
+      <c r="BK11" s="23"/>
+      <c r="BL11" s="23"/>
+      <c r="BM11" s="23"/>
+      <c r="BN11" s="23"/>
+      <c r="BO11" s="23"/>
+      <c r="BP11" s="23"/>
+      <c r="BQ11" s="23"/>
+      <c r="BR11" s="13"/>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
@@ -4404,7 +4408,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0DTS8VCFB</t>
+          <t>B0F1XRXLVK</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -4417,23 +4421,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; SofasUltrasonic Cleaning, UV-C Light &amp; Hot Air &amp; Roller</t>
+          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0DTS8VCFB</t>
+          <t>B0F1XRXLVK</t>
         </is>
       </c>
       <c r="M12" s="14"/>
@@ -4454,7 +4458,7 @@
       <c r="AB12"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="19">
-        <v>32</v>
+        <v>392</v>
       </c>
       <c r="AE12" s="15"/>
       <c r="AF12" s="21">
@@ -4510,7 +4514,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0F1XRXLVK</t>
+          <t>B0FL7M5YV1</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -4523,23 +4527,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen</t>
+          <t>Blarie Pure Sleepy Pro Bed Vacuum, 12000pa Puresleepy Pro Bed Vacuum, Mattress Cleaner Machine Deep Cleaner, 8,000 Vibrations</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FL7M5YV1?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41WjYlsDTvL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0F1XRXLVK</t>
+          <t>B0FL7M5YV1</t>
         </is>
       </c>
       <c r="M13" s="14"/>
@@ -4559,13 +4563,9 @@
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13" s="2"/>
-      <c r="AD13" s="19">
-        <v>392</v>
-      </c>
+      <c r="AD13" s="19"/>
       <c r="AE13" s="15"/>
-      <c r="AF13" s="21">
-        <v>4.4</v>
-      </c>
+      <c r="AF13" s="21"/>
       <c r="AG13" s="22">
         <v>0</v>
       </c>
@@ -4616,7 +4616,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0FL7M5YV1</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -4629,23 +4629,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Blarie Pure Sleepy Pro Bed Vacuum, 12000pa Puresleepy Pro Bed Vacuum, Mattress Cleaner Machine Deep Cleaner, 8,000 Vibrations</t>
+          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FL7M5YV1?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41WjYlsDTvL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0FL7M5YV1</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="M14" s="14"/>
@@ -4665,9 +4665,13 @@
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14" s="2"/>
-      <c r="AD14" s="19"/>
+      <c r="AD14" s="19">
+        <v>198</v>
+      </c>
       <c r="AE14" s="15"/>
-      <c r="AF14" s="21"/>
+      <c r="AF14" s="21">
+        <v>4.6</v>
+      </c>
       <c r="AG14" s="22">
         <v>0</v>
       </c>
@@ -4718,7 +4722,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0GJDH8XTW</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -4731,23 +4735,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500</t>
+          <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights,</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0GJDH8XTW</t>
         </is>
       </c>
       <c r="M15" s="14"/>
@@ -4768,11 +4772,11 @@
       <c r="AB15"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="19">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="AE15" s="15"/>
       <c r="AF15" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
@@ -4816,112 +4820,6 @@
       <c r="BP15" s="23"/>
       <c r="BQ15" s="23"/>
       <c r="BR15" s="13"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
-        <v>15</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>B0GJDH8XTW</t>
-        </is>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights,</t>
-        </is>
-      </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1</t>
-        </is>
-      </c>
-      <c r="K16" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>B0GJDH8XTW</t>
-        </is>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16"/>
-      <c r="AB16"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="19">
-        <v>30</v>
-      </c>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG16" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="20"/>
-      <c r="AI16" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ16"/>
-      <c r="AK16" s="13"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="13"/>
-      <c r="AN16" s="13"/>
-      <c r="AO16" s="13"/>
-      <c r="AP16"/>
-      <c r="AQ16" s="19"/>
-      <c r="AR16" s="19"/>
-      <c r="AS16" s="14"/>
-      <c r="AT16" s="13"/>
-      <c r="AU16" s="13"/>
-      <c r="AV16" s="14"/>
-      <c r="AW16" s="13"/>
-      <c r="AX16" s="13"/>
-      <c r="AY16" s="13"/>
-      <c r="AZ16" s="13"/>
-      <c r="BA16" s="13"/>
-      <c r="BB16" s="13"/>
-      <c r="BC16" s="13"/>
-      <c r="BD16" s="13"/>
-      <c r="BE16" s="13"/>
-      <c r="BF16" s="13"/>
-      <c r="BG16" s="13"/>
-      <c r="BH16" s="14"/>
-      <c r="BI16" s="23"/>
-      <c r="BJ16" s="23"/>
-      <c r="BK16" s="23"/>
-      <c r="BL16" s="23"/>
-      <c r="BM16" s="23"/>
-      <c r="BN16" s="23"/>
-      <c r="BO16" s="23"/>
-      <c r="BP16" s="23"/>
-      <c r="BQ16" s="23"/>
-      <c r="BR16" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4970,56 +4868,51 @@
     <hyperlink ref="L7" r:id="rId41" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V"/>
     <hyperlink ref="M7" r:id="rId42" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N7" r:id="rId43"/>
-    <hyperlink ref="C8" r:id="rId44" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
+    <hyperlink ref="C8" r:id="rId44" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
     <hyperlink ref="G8" r:id="rId45" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J8" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1"/>
-    <hyperlink ref="K8" r:id="rId47" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
-    <hyperlink ref="C9" r:id="rId49" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
+    <hyperlink ref="J8" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
+    <hyperlink ref="K8" r:id="rId47" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
+    <hyperlink ref="C9" r:id="rId49" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
     <hyperlink ref="G9" r:id="rId50" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J9" r:id="rId51" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
-    <hyperlink ref="K9" r:id="rId52" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
-    <hyperlink ref="C10" r:id="rId54" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
-    <hyperlink ref="G10" r:id="rId55" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J10" r:id="rId56" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
-    <hyperlink ref="K10" r:id="rId57" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
-    <hyperlink ref="C11" r:id="rId59" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="G11" r:id="rId60" tooltip="https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J11" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
-    <hyperlink ref="K11" r:id="rId62" tooltip="https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg"/>
-    <hyperlink ref="L11" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="M11" r:id="rId64" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
-    <hyperlink ref="N11" r:id="rId65"/>
-    <hyperlink ref="AW11" r:id="rId66" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP"/>
-    <hyperlink ref="C12" r:id="rId67" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="J9" r:id="rId51" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
+    <hyperlink ref="K9" r:id="rId52" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
+    <hyperlink ref="C10" r:id="rId54" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="G10" r:id="rId55" tooltip="https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J10" r:id="rId56" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
+    <hyperlink ref="K10" r:id="rId57" tooltip="https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg"/>
+    <hyperlink ref="L10" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="M10" r:id="rId59" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N10" r:id="rId60"/>
+    <hyperlink ref="AW10" r:id="rId61" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP"/>
+    <hyperlink ref="C11" r:id="rId62" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="G11" r:id="rId63" tooltip="https://www.amazon.co.ukundefined"/>
+    <hyperlink ref="J11" r:id="rId64" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
+    <hyperlink ref="K11" r:id="rId65" tooltip="https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId66" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="C12" r:id="rId67" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
     <hyperlink ref="G12" r:id="rId68" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J12" r:id="rId69" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
-    <hyperlink ref="K12" r:id="rId70" tooltip="https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId71" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
-    <hyperlink ref="C13" r:id="rId72" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
+    <hyperlink ref="J12" r:id="rId69" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
+    <hyperlink ref="K12" r:id="rId70" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId71" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
+    <hyperlink ref="C13" r:id="rId72" tooltip="https://www.amazon.co.uk/dp/B0FL7M5YV1"/>
     <hyperlink ref="G13" r:id="rId73" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J13" r:id="rId74" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
-    <hyperlink ref="K13" r:id="rId75" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
-    <hyperlink ref="C14" r:id="rId77" tooltip="https://www.amazon.co.uk/dp/B0FL7M5YV1"/>
+    <hyperlink ref="J13" r:id="rId74" tooltip="https://www.amazon.co.uk/dp/B0FL7M5YV1?psc=1"/>
+    <hyperlink ref="K13" r:id="rId75" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41WjYlsDTvL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B0FL7M5YV1"/>
+    <hyperlink ref="C14" r:id="rId77" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
     <hyperlink ref="G14" r:id="rId78" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J14" r:id="rId79" tooltip="https://www.amazon.co.uk/dp/B0FL7M5YV1?psc=1"/>
-    <hyperlink ref="K14" r:id="rId80" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41WjYlsDTvL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B0FL7M5YV1"/>
-    <hyperlink ref="C15" r:id="rId82" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="J14" r:id="rId79" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
+    <hyperlink ref="K14" r:id="rId80" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="C15" r:id="rId82" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
     <hyperlink ref="G15" r:id="rId83" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J15" r:id="rId84" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K15" r:id="rId85" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="C16" r:id="rId87" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
-    <hyperlink ref="G16" r:id="rId88" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J16" r:id="rId89" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
-    <hyperlink ref="K16" r:id="rId90" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
+    <hyperlink ref="J15" r:id="rId84" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
+    <hyperlink ref="K15" r:id="rId85" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
   </hyperlinks>
-  <drawing r:id="rId92"/>
+  <drawing r:id="rId87"/>
 </worksheet>
 </file>
 
